--- a/Data/EXCEL/Transfer/salemon/202206/2761-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/2761-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{727B3BC6-5B2E-4DC5-A203-076242863E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FA769061-D8C6-4F75-87D2-0B7DD3311D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="2761-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,21 +1218,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.125" customWidth="1"/>
-    <col min="2" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="12.125" customWidth="1"/>
-    <col min="7" max="7" width="10.5" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="10" width="10.5" customWidth="1"/>
-    <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="10.5" customWidth="1"/>
-    <col min="13" max="13" width="11" customWidth="1"/>
-    <col min="14" max="15" width="10.5" customWidth="1"/>
-    <col min="16" max="16" width="11" customWidth="1"/>
-    <col min="17" max="17" width="11.75" customWidth="1"/>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="5" width="12.625" customWidth="1"/>
+    <col min="6" max="6" width="13.875" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="12.625" customWidth="1"/>
+    <col min="9" max="10" width="12" customWidth="1"/>
+    <col min="11" max="11" width="12.625" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+    <col min="14" max="15" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1385,166 +1385,166 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>38.75</v>
+        <v>41</v>
       </c>
       <c r="C5" s="7">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D5" s="7">
-        <v>42.15</v>
+        <v>41.45</v>
       </c>
       <c r="E5" s="7">
-        <v>37.700000000000003</v>
+        <v>37.6</v>
       </c>
       <c r="F5" s="8">
-        <v>2.25</v>
+        <v>-2</v>
       </c>
       <c r="G5" s="8">
-        <v>5.81</v>
+        <v>-4.88</v>
       </c>
       <c r="H5" s="9">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="I5" s="8">
-        <v>13.8</v>
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="I5" s="10">
+        <v>31.3</v>
       </c>
       <c r="J5" s="10">
-        <v>-5.87</v>
+        <v>55.6</v>
       </c>
       <c r="K5" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="L5" s="10">
-        <v>-8.39</v>
+        <v>2.97</v>
+      </c>
+      <c r="L5" s="8">
+        <v>-2.0699999999999998</v>
       </c>
       <c r="M5" s="9">
-        <v>0.35499999999999998</v>
-      </c>
-      <c r="N5" s="8">
-        <v>13.8</v>
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="N5" s="10">
+        <v>31.3</v>
       </c>
       <c r="O5" s="10">
-        <v>-5.87</v>
+        <v>55.6</v>
       </c>
       <c r="P5" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="Q5" s="10">
-        <v>-8.39</v>
+        <v>2.97</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>-2.0699999999999998</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>56.9</v>
+        <v>38.75</v>
       </c>
       <c r="C6" s="7">
-        <v>38.75</v>
+        <v>41</v>
       </c>
       <c r="D6" s="7">
-        <v>61</v>
+        <v>42.15</v>
       </c>
       <c r="E6" s="7">
-        <v>37.049999999999997</v>
+        <v>37.700000000000003</v>
       </c>
       <c r="F6" s="10">
-        <v>-18.149999999999999</v>
+        <v>2.25</v>
       </c>
       <c r="G6" s="10">
-        <v>-31.9</v>
+        <v>5.81</v>
       </c>
       <c r="H6" s="9">
-        <v>0.312</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="I6" s="10">
-        <v>-48</v>
-      </c>
-      <c r="J6" s="10">
-        <v>-46.6</v>
+        <v>13.8</v>
+      </c>
+      <c r="J6" s="8">
+        <v>-5.87</v>
       </c>
       <c r="K6" s="9">
-        <v>2.15</v>
-      </c>
-      <c r="L6" s="10">
-        <v>-8.7899999999999991</v>
+        <v>2.5</v>
+      </c>
+      <c r="L6" s="8">
+        <v>-8.39</v>
       </c>
       <c r="M6" s="9">
-        <v>0.312</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="N6" s="10">
-        <v>-48</v>
-      </c>
-      <c r="O6" s="10">
-        <v>-46.6</v>
+        <v>13.8</v>
+      </c>
+      <c r="O6" s="8">
+        <v>-5.87</v>
       </c>
       <c r="P6" s="9">
-        <v>2.15</v>
-      </c>
-      <c r="Q6" s="10">
-        <v>-8.7899999999999991</v>
+        <v>2.5</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>-8.39</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="9" t="s">
-        <v>17</v>
+        <v>44652</v>
+      </c>
+      <c r="B7" s="7">
+        <v>56.9</v>
+      </c>
+      <c r="C7" s="7">
+        <v>38.75</v>
+      </c>
+      <c r="D7" s="7">
+        <v>61</v>
+      </c>
+      <c r="E7" s="7">
+        <v>37.049999999999997</v>
+      </c>
+      <c r="F7" s="8">
+        <v>-18.149999999999999</v>
+      </c>
+      <c r="G7" s="8">
+        <v>-31.9</v>
       </c>
       <c r="H7" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="I7" s="10">
-        <v>-2.1</v>
+        <v>0.312</v>
+      </c>
+      <c r="I7" s="8">
+        <v>-48</v>
       </c>
       <c r="J7" s="8">
-        <v>2.52</v>
+        <v>-46.6</v>
       </c>
       <c r="K7" s="9">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="L7" s="8">
-        <v>3.68</v>
+        <v>-8.7899999999999991</v>
       </c>
       <c r="M7" s="9">
-        <v>0.6</v>
-      </c>
-      <c r="N7" s="10">
-        <v>-2.1</v>
+        <v>0.312</v>
+      </c>
+      <c r="N7" s="8">
+        <v>-48</v>
       </c>
       <c r="O7" s="8">
-        <v>2.52</v>
+        <v>-46.6</v>
       </c>
       <c r="P7" s="9">
-        <v>1.84</v>
+        <v>2.15</v>
       </c>
       <c r="Q7" s="8">
-        <v>3.68</v>
+        <v>-8.7899999999999991</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>17</v>
@@ -1565,86 +1565,139 @@
         <v>17</v>
       </c>
       <c r="H8" s="9">
-        <v>0.61299999999999999</v>
-      </c>
-      <c r="I8" s="10">
-        <v>-1.65</v>
-      </c>
-      <c r="J8" s="8">
-        <v>2.71</v>
+        <v>0.6</v>
+      </c>
+      <c r="I8" s="8">
+        <v>-2.1</v>
+      </c>
+      <c r="J8" s="10">
+        <v>2.52</v>
       </c>
       <c r="K8" s="9">
-        <v>1.24</v>
-      </c>
-      <c r="L8" s="8">
-        <v>4.25</v>
+        <v>1.84</v>
+      </c>
+      <c r="L8" s="10">
+        <v>3.68</v>
       </c>
       <c r="M8" s="9">
-        <v>0.61299999999999999</v>
-      </c>
-      <c r="N8" s="10">
-        <v>-1.65</v>
-      </c>
-      <c r="O8" s="8">
-        <v>2.71</v>
+        <v>0.6</v>
+      </c>
+      <c r="N8" s="8">
+        <v>-2.1</v>
+      </c>
+      <c r="O8" s="10">
+        <v>2.52</v>
       </c>
       <c r="P8" s="9">
-        <v>1.24</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>4.25</v>
+        <v>1.84</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>3.68</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
+        <v>44593</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="9">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="I9" s="8">
+        <v>-1.65</v>
+      </c>
+      <c r="J9" s="10">
+        <v>2.71</v>
+      </c>
+      <c r="K9" s="9">
+        <v>1.24</v>
+      </c>
+      <c r="L9" s="10">
+        <v>4.25</v>
+      </c>
+      <c r="M9" s="9">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="N9" s="8">
+        <v>-1.65</v>
+      </c>
+      <c r="O9" s="10">
+        <v>2.71</v>
+      </c>
+      <c r="P9" s="9">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>44562</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="9">
+      <c r="B10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="9">
         <v>0.623</v>
       </c>
-      <c r="I9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="8">
+      <c r="I10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="10">
         <v>5.8</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K10" s="9">
         <v>0.623</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L10" s="10">
         <v>5.8</v>
       </c>
-      <c r="M9" s="9">
+      <c r="M10" s="9">
         <v>0.623</v>
       </c>
-      <c r="N9" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="O9" s="8">
+      <c r="N10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O10" s="10">
         <v>5.8</v>
       </c>
-      <c r="P9" s="9">
+      <c r="P10" s="9">
         <v>0.623</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q10" s="10">
         <v>5.8</v>
       </c>
     </row>
